--- a/data/2026/29-neamt/120726-piatra-neamt/budget_file.xlsx
+++ b/data/2026/29-neamt/120726-piatra-neamt/budget_file.xlsx
@@ -707,9 +707,10 @@
           <t>11.02.02</t>
         </is>
       </c>
-      <c r="C9">
-        <f>Sume defalcate din TVA pt finantarea cheltuielilor descentralizate la nivelul judetelor, oraelor, comunelor si municipiului Bucuresti, din care:</f>
-        <v/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>=Sume defalcate din TVA pt finantarea cheltuielilor descentralizate la nivelul judetelor, oraelor, comunelor si municipiului Bucuresti, din care:</t>
+        </is>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -734,9 +735,10 @@
           <t>11.02.06</t>
         </is>
       </c>
-      <c r="C10">
-        <f>Sume defalcate din TVA pt echilibrarea bugetelor locale</f>
-        <v/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>=Sume defalcate din TVA pt echilibrarea bugetelor locale</t>
+        </is>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -761,9 +763,10 @@
           <t>11.02.09</t>
         </is>
       </c>
-      <c r="C11">
-        <f>Sume defalcate din TVA pt finantarea învățământului particular sau confesional acreditat</f>
-        <v/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>=Sume defalcate din TVA pt finantarea învățământului particular sau confesional acreditat</t>
+        </is>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1570,26 +1573,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>71.81</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL RAMBURSARI DE CREDITE</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" s="3" t="n">
-        <v>1660108608</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '1.660,10 8.608,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -4108,9 +4116,7 @@
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G118" s="8" t="n">
-        <v>24613006920</v>
-      </c>
+      <c r="G118" s="8" t="n"/>
       <c r="H118" s="6" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -4118,7 +4124,7 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>code 60.61 (expense_functional) not in nomenclator</t>
+          <t>unparseable cell '24.613,00 6.920,00' in column total_2026; code 60.61 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5010,7 +5016,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5019,28 +5025,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>48.02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (18%): 'VENITURI PROPRII' vs 'Sume primite de la UE/alti donatori in c'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5049,28 +5050,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.88.02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 66.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5079,42 +5075,32 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.89.02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 67.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5123,14 +5109,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell 'PROPUNERI BUGET 2026' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5139,42 +5125,32 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (30%): 'CHELTUIELI - TOTAL (cod 51.02 + 54.02 + ' vs 'Partea I-a SERVICII PUBLICE GENERALE'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5183,7 +5159,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '1.660,10 8.608,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -5199,16 +5175,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'VENITURI PROPRII' vs 'Sume primite de la UE/alti donatori in c'</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -5224,66 +5200,71 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.02.88.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
+          <t>name mismatch vs nomenclator (21%): 'COMISIOANE' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.02.89.02</t>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
+          <t>61.02 total_2026: parent 11.118,00 != sum(children) 584,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>59</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>unparseable cell 'PROPUNERI BUGET 2026' in column total_2026</t>
+          <t>name mismatch vs nomenclator (16%): 'FOND HANDICAP' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5284,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'CHELTUIELI - TOTAL (cod 51.02 + 54.02 + ' vs 'Partea I-a SERVICII PUBLICE GENERALE'</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -5328,24 +5309,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (30%): 'AJUTOARE SOCIALE - finanțarea drepturilo' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5353,24 +5334,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): 'COMISIOANE' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>66.02 total_2026: parent 16.992,00 != sum(children) 6.975,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5378,29 +5364,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 11.118,00 != sum(children) 584,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (49%): 'AJUTOARE SOCIALE IN NATURA' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5408,37 +5389,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (16%): 'FOND HANDICAP' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>code 71.85 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>67.02 total_2026: parent 38.905,10 != sum(children) 6.250,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5440,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5463,37 +5449,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'AJUTOARE SOCIALE - finanțarea drepturilo' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
+          <t>name mismatch vs nomenclator (47%): 'AJUTOARE SOCIALE' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 16.992,00 != sum(children) 6.975,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (50%): 'PROGRAME CU FINANTARE NERAMBURSABILA' vs 'TITLUL X PROIECTE CU FINANTARE DIN FONDU'</t>
         </is>
       </c>
     </row>
@@ -5509,53 +5490,53 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (49%): 'AJUTOARE SOCIALE IN NATURA' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
+          <t>name mismatch vs nomenclator (37%): 'SPORT+ALTE ACTIUNI SOCIAL-CULTURALE' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>code 71.85 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5563,29 +5544,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 38.905,10 != sum(children) 6.250,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (28%): 'Servicii recreative si sportive' vs 'Sport'</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5593,12 +5569,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (47%): 'AJUTOARE SOCIALE' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
+          <t>68.02 total_2026: parent 77.978,50 != sum(children) 35.594,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -5643,12 +5624,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'SPORT+ALTE ACTIUNI SOCIAL-CULTURALE' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>name mismatch vs nomenclator (50%): 'ASISTENTA SOCIALA: AJUTOARE SOCIALE + IN' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
         </is>
       </c>
     </row>
@@ -5680,12 +5661,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5693,19 +5674,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Servicii recreative si sportive' vs 'Sport'</t>
+          <t>70.02 total_2026: parent 90.318,50 != sum(children) 90.272,50 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -5716,11 +5702,6 @@
       <c r="C28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -5728,19 +5709,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 77.978,50 != sum(children) 35.594,00 (3 children)</t>
+          <t>unparseable cell '24.613,00 6.920,00' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5748,12 +5729,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60.61</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'PROGRAME CU FINANTARE NERAMBURSABILA' vs 'TITLUL X PROIECTE CU FINANTARE DIN FONDU'</t>
+          <t>code 60.61 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -5773,24 +5754,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'ASISTENTA SOCIALA: AJUTOARE SOCIALE + IN' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5798,12 +5779,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>58.71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>code 58.71 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -5819,11 +5800,11 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5833,32 +5814,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.02 total_2026: parent 90.318,50 != sum(children) 90.272,50 (3 children)</t>
+          <t>84.02 total_2026: parent 38.453,50 != sum(children) 2.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>code 60.61 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (46%): 'Ssue  r d oee aee u nr' vs 'Subvenţii pentru acoperirea diferenţelor'</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5855,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5883,135 +5864,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (33%): 'CHELTUIELI DE CAPITAL Din total capitol ' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>58.71</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
-        <is>
-          <t>code 58.71 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>84.02 total_2026: parent 38.453,50 != sum(children) 2.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (46%): 'Ssue  r d oee aee u nr' vs 'Subvenţii pentru acoperirea diferenţelor'</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (33%): 'CHELTUIELI DE CAPITAL Din total capitol ' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>96.02</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (0%): '' vs 'Partea a VII-a REZERVE, EXCEDENT/DEFICIT'</t>
         </is>
@@ -6028,7 +5904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6050,7 +5926,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -6060,60 +5936,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>133</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>102</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fd5cdbde2e0077d9091cceb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>42167e06fc08ab248cb200ee268bf29ba0a02f0dd490d40d9615340eded9e7bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-4, 144 linii</t>
         </is>

--- a/data/2026/29-neamt/120726-piatra-neamt/budget_file.xlsx
+++ b/data/2026/29-neamt/120726-piatra-neamt/budget_file.xlsx
@@ -70,16 +70,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,12 +459,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -537,7 +551,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>VENITURI PROPRII</t>
         </is>
@@ -551,7 +565,7 @@
           <t>revenue</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>243944.27</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -573,7 +587,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1. VENITURI IMPOZITE SI TAXE</t>
+          <t>I . VENITURI IMPOZITE SI TAXE</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -595,9 +609,9 @@
           <t>04.02</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>COTE SI SUME DEFALCATE DIN IMPOZITUL PE VENIT</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>COTE ŞI SUME DEFALCATE DIN IMPOZITUL PE VENIT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -623,9 +637,9 @@
           <t>04.02.01</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>A. Cote defalcate din impozitul pe venit (63 %)</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>A. Cote defalcate din impozitul pe venit ( 63 % )</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -645,13 +659,13 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>04.02.04</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>B. Sume alocate de consiliul judetean pt echilibrarea bugetelor locale</t>
         </is>
@@ -673,13 +687,13 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>11.02</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>SUME DEFALCATE DIN TAXA PE VALOAREA ADĂUGATĂ PENTRU BUGETELE LOCALE</t>
         </is>
@@ -701,15 +715,15 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>11.02.02</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>=Sume defalcate din TVA pt finantarea cheltuielilor descentralizate la nivelul judetelor, oraelor, comunelor si municipiului Bucuresti, din care:</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>=Sume defalcate din TVA pt finantarea cheltuielilor descentralizate la nivelul judetelor, orașelor, comunelor si municipiului Bucuresti, din care:</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -735,7 +749,7 @@
           <t>11.02.06</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>=Sume defalcate din TVA pt echilibrarea bugetelor locale</t>
         </is>
@@ -757,13 +771,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>11.02.09</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>=Sume defalcate din TVA pt finantarea învățământului particular sau confesional acreditat</t>
         </is>
@@ -793,7 +807,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>II. VENITURI DIN CAPITAL</t>
+          <t>II . VENITURI DIN CAPITAL</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -801,7 +815,7 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" s="3" t="n">
-        <v>6609</v>
+        <v>60.99</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -815,7 +829,7 @@
           <t>42.02</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>III. SUBVENTII</t>
         </is>
@@ -837,15 +851,15 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>42.02.34</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Subventii pentru acordarea ajutorului pentru încălzirea locuinței și a suplimentului pentru energie alocate pentru consumul de combustibili solizi și/sau petrolieri</t>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>_Subventii pentru acordarea ajutorului pentru încălzirea locuinței și a suplimentului pentru energie alocate pentru consumul de combustibili solizi şi/sau petrolieri</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -871,9 +885,9 @@
           <t>42.02.41</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Subventii din bugetul de stat pentru finantarea sanatatii</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>_Subventii din bugetul de stat pentru finantarea sanatatii</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -893,15 +907,15 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>42.02.66</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Subvenții din bugetul de stat alocate conform contractelor încheiate cu direcțiile de sănătate publică</t>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>_Subvenţii din bugetul de stat alocate conform contractelor încheiate cu direcţiile de sănătate publică</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -921,15 +935,15 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>42.02.88</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Alocări de sume din PNRR aferente asistenței financiare nerambursabile (cod 42.02.88 01 la 42.02.88.04)</t>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Alocări de sume din PNRR aferente asistenței financiare nerambursabile ( cod 42.02.88 01 la 42.02.88.04)</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -955,9 +969,9 @@
           <t>42.02.88.01</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Fonduri europene nerambursabile</t>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>_Fonduri europene nerambursabile</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -984,9 +998,9 @@
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Sume aferente TVA</t>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>_Sume aferente TVA</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
@@ -998,7 +1012,7 @@
           <t>revenue</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <v>9855</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1008,19 +1022,19 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>name mismatch vs nomenclator (31%): '_Sume aferente TVA' vs 'Finantare publica naționala'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>42.02.89</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Alocări de sume din PNRR aferente componentei împrumuturi (cod42.02.89.01 la 42.02.89.03)</t>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Alocări de sume din PNRR aferente componentei împrumuturi ( cod 42.02.89.01 la 42.02.89.03)</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1046,9 +1060,9 @@
           <t>42.02.89.01</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Fonduri din împrumut rambursabil</t>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>_Fonduri din împrumut rambursabil</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1075,9 +1089,9 @@
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Sume aferente TVA</t>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>_Sume aferente TVA</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
@@ -1089,7 +1103,7 @@
           <t>revenue</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="6" t="n">
         <v>1201</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1099,19 +1113,19 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>name mismatch vs nomenclator (31%): '_Sume aferente TVA' vs 'Finantare publica naționala'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>42.02.93</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Sue i oi    e    e  de e din FEN postaderare, aferente perioadei de programare 2021-2027</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Subvenţii de la bugetul de stat către bugetele locale necesare susţinerii derulării proiectelor finanţate din FEN postaderare, aferente perioadei de programare 2021-2027</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1150,15 +1164,15 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>43.02.34</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Sume alocate din bugetul ANCPI pentru finanțarea lucrărilor de înregistrare sistematică din cadrul Programului național de cadastru și carte funciară</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>_Sume alocate din bugetul ANCPI pentru finanțarea lucrărilor de înregistrare sistematică din cadrul Programului național de cadastru și carte funciară</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1178,15 +1192,15 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>43.02.44</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sume alocate din sumele obținute în urma scoaterii la licitație a certificatelor de emisii de gaze cu efect de seră pentru finanțarea proiectelor de investiții</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>_Sume alocate din sumele obținute în urma scoaterii la licitație a certificatelor de emisii de gaze cu efect de seră pentru finanțarea proiectelor de investiții</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,15 +1220,15 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>43.02.49</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sume alocate din PNRR aferente asistenței financiare nerambursabile (cod 43.02.49.01 la 43.02.49.03)</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Sume alocate din PNRR aferente asistenței financiare nerambursabile ( cod 43.02.49.01 la 43.02.49.03)</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1240,9 +1254,9 @@
           <t>43.02.49.01</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Fonduri europene nerambursabile</t>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>_Fonduri europene nerambursabile</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1268,9 +1282,9 @@
           <t>43.02.49.03</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sume aferente TVA</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>_Sume aferente TVA</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,9 +1310,9 @@
           <t>45.02</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>V.SUME PRIMITE DE LA UE IN CONTUL PLATILOR EFECTUATE</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>V. SUME PRIMITE DE LA UE IN CONTUL PLATILOR EFECTUATE</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1319,40 +1333,40 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>DENUMIREA INDICATORILOR</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n">
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>unparseable cell 'PROPUNERI BUGET 2026' in column total_2026</t>
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>50.02</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>CHELTUIELI - TOTAL (cod 51.02 + 54.02 + 55.02 + 61.02 + 65.02 + 66.02 + 67.02 + 68.02 + 70.02 + 74.02 + 80.02 + 81.02 + 84.02)</t>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>CHELTUIELI - TOTAL (cod 51.02 + 54.02 + 55.02 + 61.02 + 65.02 + 66.02 + 67.02 + 68.02 + 70.02 + 74.02 + 80.02 + 81.02 + 84.02 )</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
@@ -1364,7 +1378,7 @@
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="6" t="n">
         <v>493008.7</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1384,7 +1398,7 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>AUTORITATI PUBLICE</t>
         </is>
@@ -1417,7 +1431,7 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE PERSONAL</t>
         </is>
@@ -1469,7 +1483,7 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI MATERIALE SI SERVICII</t>
         </is>
@@ -1492,7 +1506,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>PRIMARIA</t>
+        </is>
+      </c>
       <c r="E37" t="n">
         <v>2</v>
       </c>
@@ -1517,7 +1535,7 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>ALTE CHELTUIELI</t>
         </is>
@@ -1539,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>60</t>
@@ -1550,7 +1568,7 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
         </is>
@@ -1573,35 +1591,39 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>71.81</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>CHELTUIELI DE CAPITAL RAMBURSARI DE CREDITE</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>unparseable cell '1.660,10 8.608,00' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+          <t>RAMBURSARI DE CREDITE</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>8608</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>85</t>
@@ -1612,7 +1634,7 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
         </is>
@@ -1635,7 +1657,7 @@
     <row r="42">
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Primăria Municipiului Piatra Neam</t>
+          <t>Primăria Municipiului Piatra Neamţ</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1657,7 +1679,7 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SERVICII PUBLICE GENERALE</t>
         </is>
@@ -1690,7 +1712,7 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE PERSONAL</t>
         </is>
@@ -1723,7 +1745,7 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI MATERIALE SI SERVICII</t>
         </is>
@@ -1756,7 +1778,7 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>FOND DE REZERVA BUGETARA</t>
         </is>
@@ -1789,7 +1811,7 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>FOND HANDICAP</t>
         </is>
@@ -1822,7 +1844,7 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
@@ -1836,7 +1858,7 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="G48" s="6" t="n">
         <v>1100</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -1850,7 +1872,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>85</t>
@@ -1861,7 +1883,7 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
         </is>
@@ -1887,7 +1909,7 @@
           <t>54.02.05</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>FOND REZERVA BUGETARA</t>
         </is>
@@ -1915,7 +1937,7 @@
           <t>54.02.10</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>SERVICII PUBLICE GENERALE-EVIDENTA POPULATIEI</t>
         </is>
@@ -1943,7 +1965,7 @@
           <t>54.02.50</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>ALTE SERVICII PUBLICE GENERALE</t>
         </is>
@@ -1971,7 +1993,7 @@
           <t>55.02</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>DATORIA PUBLICA - DOBANZI</t>
         </is>
@@ -2004,7 +2026,7 @@
           <t>55.02</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>COMISIOANE</t>
         </is>
@@ -2018,7 +2040,7 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="G54" s="6" t="n">
         <v>27</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2043,7 +2065,7 @@
           <t>55.02</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>DOBANZI</t>
         </is>
@@ -2066,35 +2088,35 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>61.02</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
         </is>
       </c>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G56" s="8" t="n">
+      <c r="G56" s="10" t="n">
         <v>11118</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>61.02 total_2026: parent 11.118,00 != sum(children) 584,00 (1 children)</t>
         </is>
@@ -2111,7 +2133,7 @@
           <t>61.02</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE PERSONAL</t>
         </is>
@@ -2144,7 +2166,7 @@
           <t>61.02</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI MATERIALE SI SERVICII</t>
         </is>
@@ -2177,7 +2199,7 @@
           <t>61.02</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>FOND HANDICAP</t>
         </is>
@@ -2191,7 +2213,7 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="G59" s="6" t="n">
         <v>4</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -2216,7 +2238,7 @@
           <t>61.02</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
@@ -2230,7 +2252,7 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="G60" s="6" t="n">
         <v>526</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -2244,7 +2266,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>85</t>
@@ -2255,7 +2277,7 @@
           <t>61.02</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
         </is>
@@ -2281,9 +2303,9 @@
           <t>61.02.03.04</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>POLITIA LOCALÃ</t>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>POLITIA LOCALĂ</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2309,7 +2331,7 @@
           <t>61.02.05</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>PROTECTIE CIVILA</t>
         </is>
@@ -2337,7 +2359,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>INVATAMANT</t>
         </is>
@@ -2370,7 +2392,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE PERSONAL</t>
         </is>
@@ -2403,7 +2425,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI MATERIALE SI SERVICII</t>
         </is>
@@ -2436,7 +2458,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>TRANSFERURI - finanțarea învățământului particular</t>
         </is>
@@ -2458,7 +2480,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
           <t>57</t>
@@ -2469,7 +2491,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>AJUTOARE SOCIALE - finanțarea drepturilor copiilor cu cerințe educaționale speciale, tichete soc, transport</t>
         </is>
@@ -2483,7 +2505,7 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="G68" s="6" t="n">
         <v>7542</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -2508,7 +2530,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>FOND HANDICAP</t>
         </is>
@@ -2530,7 +2552,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="30" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>56</t>
@@ -2541,7 +2563,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
         </is>
@@ -2563,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="30" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>60</t>
@@ -2574,7 +2596,7 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
         </is>
@@ -2597,350 +2619,377 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71.85</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE CAPITAL PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>2</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" s="3" t="n">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>CHELTUIELI DE CAPITAL</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="n">
         <v>2751</v>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>TOTAL CHELTUIELI ÎN DOMENIUL ÎNVÄTÄMÂNTULUI</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="n">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL CHELTUIELI ÎN DOMENIUL ÎNVĂȚĂMÂNTULUI</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
         <v>138149</v>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>SANATATE</t>
         </is>
       </c>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G74" s="8" t="n">
+      <c r="G75" s="10" t="n">
         <v>16992</v>
       </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>66.02 total_2026: parent 16.992,00 != sum(children) 6.975,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE PERSONAL</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>2</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>6082</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>66.02 total_2026: parent 16.992,00 != sum(children) 10.002,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>CHELTUIELI DE PERSONAL</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>6082</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI MATERIALE SI SERVICII</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>2</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="n">
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
         <v>785</v>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>AJUTOARE SOCIALE IN NATURA</t>
         </is>
       </c>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="n">
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (49%): 'AJUTOARE SOCIALE IN NATURA' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>59.40</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>FOND HANDICAP</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>59.40</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>FOND HANDICAP</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>2</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="n">
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
         <v>10002</v>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>71.85</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="n"/>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>code 71.85 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>66.02.06.01</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol : Spitale generale</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>2</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="n">
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
         <v>10002</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>66.02.08</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Servicii de sanatate publică (cabinete medicale școlare)</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>3</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>6975</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -2951,142 +3000,124 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>66.02.06.01</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Spitale generale</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>66.02.08</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Servicii de sanatate publică (cabinete medicale școlare)</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>6975</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>66.02.50.50</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Alte institutii si actiuni sanitare (centre de permanență, drepturi donatori sânge)</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>3</v>
-      </c>
-      <c r="F83" t="inlineStr">
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G83" s="3" t="n">
+      <c r="G85" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>CULTURA, RELIGIE SI RECREERE</t>
         </is>
       </c>
-      <c r="D84" s="6" t="n"/>
-      <c r="E84" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G84" s="8" t="n">
+      <c r="G86" s="10" t="n">
         <v>38905.1</v>
       </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>67.02 total_2026: parent 38.905,10 != sum(children) 6.250,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>CHELTUIELI MATERIALE SI SERVICII</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>3</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>AJUTOARE SOCIALE</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (47%): 'AJUTOARE SOCIALE' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3094,9 +3125,9 @@
           <t>67.02</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>CHELTUIELI MATERIALE SI SERVICII</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3108,7 +3139,7 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>8088</v>
+        <v>12000</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3119,7 +3150,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -3127,9 +3158,9 @@
           <t>67.02</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>PROGRAME CU FINANTARE NERAMBURSABILA</t>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>AJUTOARE SOCIALE</t>
         </is>
       </c>
       <c r="D88" s="4" t="n"/>
@@ -3141,8 +3172,8 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G88" s="5" t="n">
-        <v>3608</v>
+      <c r="G88" s="6" t="n">
+        <v>250</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -3151,53 +3182,47 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'PROGRAME CU FINANTARE NERAMBURSABILA' vs 'TITLUL X PROIECTE CU FINANTARE DIN FONDU'</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
+          <t>name mismatch vs nomenclator (47%): 'AJUTOARE SOCIALE' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>SPORT+ALTE ACTIUNI SOCIAL-CULTURALE</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (37%): 'SPORT+ALTE ACTIUNI SOCIAL-CULTURALE' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>8088</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -3205,9 +3230,9 @@
           <t>67.02</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE CAPITAL</t>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>PROGRAME CU FINANTARE NERAMBURSABILA</t>
         </is>
       </c>
       <c r="D90" s="4" t="n"/>
@@ -3219,8 +3244,8 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G90" s="5" t="n">
-        <v>5959.1</v>
+      <c r="G90" s="6" t="n">
+        <v>3608</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -3229,51 +3254,63 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (50%): 'PROGRAME CU FINANTARE NERAMBURSABILA' vs 'TITLUL X PROIECTE CU FINANTARE DIN FONDU'</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>3</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="n"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>SPORT+ALTE ACTIUNI SOCIAL-CULTURALE</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (37%): 'SPORT+ALTE ACTIUNI SOCIAL-CULTURALE' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n"/>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Servicii recreative si sportive</t>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
       <c r="D92" s="4" t="n"/>
@@ -3282,534 +3319,544 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>5959.1</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>67.02.05.01</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Servicii recreative si sportive</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G92" s="5" t="n">
+      <c r="G94" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (28%): 'Servicii recreative si sportive' vs 'Sport'</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>67.02.05.03</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Intretinere, gradini publice, pacuri, zone verzi si de agrement</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" t="inlineStr">
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G93" s="3" t="n">
+      <c r="G95" s="3" t="n">
         <v>29655.1</v>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>67.02.06</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Servicii religioase</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>3</v>
-      </c>
-      <c r="F94" t="inlineStr">
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G94" s="3" t="n">
+      <c r="G96" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>67.02.50</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Alte servicii in domeniile culturii, recreere si religiei</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>3</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>5750</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="n">
-        <v>77978.5</v>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>68.02 total_2026: parent 77.978,50 != sum(children) 35.594,00 (3 children)</t>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
+          <t>67.02.50</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Alte servicii in domeniile culturii, recreere si religiei</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>5750</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE PERSONAL</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>3</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>26817</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>CHELTUIELI MATERIALE SI SERVICII</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>8954.5</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>77978.5</v>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>68.02 total_2026: parent 77.978,50 != sum(children) 35.594,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>CHELTUIELI DE PERSONAL</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>26817</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>CHELTUIELI MATERIALE SI SERVICII</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>3</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>8954.5</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>TRANSFERURI</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>3</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>PROGRAME CU FINANTARE NERAMBURSABILA</t>
         </is>
       </c>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="n"/>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (50%): 'PROGRAME CU FINANTARE NERAMBURSABILA' vs 'TITLUL X PROIECTE CU FINANTARE DIN FONDU'</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>ASISTENTA SOCIALA: AJUTOARE SOCIALE + INDEMNIZATII PERSOANE CU HANDICAP</t>
         </is>
       </c>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="n">
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="n">
         <v>35792</v>
       </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (50%): 'ASISTENTA SOCIALA: AJUTOARE SOCIALE + IN' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>59.40</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>FOND HANDICAP</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>3</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>335</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Proiecte cu finantare din Fonduri exteme nerambursabile (FEN) postaderare</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>3</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>3676</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>59.40</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>FOND HANDICAP</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>3676</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
         </is>
       </c>
-      <c r="E104" t="n">
-        <v>3</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="n">
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
         <v>2123</v>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D105" s="4" t="n"/>
-      <c r="E105" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="n">
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="n">
         <v>281</v>
       </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>3</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="n"/>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>68.02.04</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Asistenta acordata persoanelor in varsta</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>3</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>6444</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>68.02.05.02</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Asistenta sociala in caz de boli si invaliditati</t>
-        </is>
-      </c>
       <c r="E108" t="n">
         <v>3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>41040</v>
-      </c>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -3819,12 +3866,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>68.02.06</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Asistenta pt familie si copii</t>
+          <t>68.02.04</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Asistenta acordata persoanelor in varsta</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3836,7 +3883,7 @@
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>10559</v>
+        <v>6444</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3847,12 +3894,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>68.02.15.01</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ajutor social</t>
+          <t>68.02.05.02</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>Asistenta sociala in caz de boli si invaliditati</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3864,7 +3911,7 @@
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>440</v>
+        <v>41040</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3875,12 +3922,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>68.02.15.02</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Cantina sociala</t>
+          <t>68.02.06</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Asistenta pt familie si copii</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3892,7 +3939,7 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>904.5</v>
+        <v>10559</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -3903,136 +3950,126 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>68.02.15.01</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>Ajutor social</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>68.02.15.02</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Cantina sociala</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>904.5</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>68.02.50</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>Alte cheltuieli in domeniul asigurarilor si asistentei sociale</t>
         </is>
       </c>
-      <c r="E112" t="n">
-        <v>3</v>
-      </c>
-      <c r="F112" t="inlineStr">
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G112" s="3" t="n">
+      <c r="G114" s="3" t="n">
         <v>18591</v>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>LOCUINTE,SERVICII SI DEZVOLTARE PUBLICA</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n"/>
-      <c r="E113" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F113" s="6" t="inlineStr">
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G113" s="8" t="n">
+      <c r="G115" s="10" t="n">
         <v>90318.5</v>
       </c>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>70.02 total_2026: parent 90.318,50 != sum(children) 90.272,50 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE PERSONAL</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>3</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>650</v>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>CHELTUIELI MATERIALE I SERVICII</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>3</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>21672.5</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>59.40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4040,9 +4077,9 @@
           <t>70.02</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>FOND HANDICAP</t>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -4054,7 +4091,7 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>36</v>
+        <v>650</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4065,189 +4102,195 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>CHELTUIELI MATERIALE ȘI SERVICII</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>21672.5</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>59.40</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>FOND HANDICAP</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>ALTE TRANSFERURI</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v>3</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="n">
+      <c r="E119" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="45" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t>60.61</t>
         </is>
       </c>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentà PNRR Proiecte cu finanțare din sumele aferente componentei de împrumuturi a PNRR</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G118" s="8" t="n"/>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>unparseable cell '24.613,00 6.920,00' in column total_2026; code 60.61 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="B120" s="8" t="n"/>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR Proiecte cu finanțare din sumele aferente componentei de împrumuturi a PNRR</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" s="8" t="inlineStr"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>unparseable cell '24.613,00 6.920,00' in column total_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>60.61</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D119" s="4" t="n"/>
-      <c r="E119" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="n">
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="n">
         <v>36381</v>
       </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>60.61</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>PLATI EFECTUATE IN ANI PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol :</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>3</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>70.02.03</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Locuinte</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>3</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>33570.5</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>70.02.05.01</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Alimentare cu apa</t>
-        </is>
-      </c>
       <c r="E122" t="n">
         <v>3</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>46</v>
-      </c>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -4257,12 +4300,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>70.02.06</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Iluminat public si electrificari rurale</t>
+          <t>70.02.03</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>Locuinte</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4274,7 +4317,7 @@
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>16465</v>
+        <v>33570.5</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4285,12 +4328,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>70.02.50</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Alte servicii in domeniile locuintelor, serviciilor si dezvoltarii comunale</t>
+          <t>70.02.05.01</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Alimentare cu apa</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4302,7 +4345,7 @@
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>40237</v>
+        <v>46</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4313,12 +4356,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>PROTECTIA MEDIULUI</t>
+          <t>70.02.06</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Iluminat public si electrificari rurale</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4330,7 +4373,7 @@
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>9928</v>
+        <v>16465</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4338,20 +4381,15 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="30" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>CHELTUIELI MATERIALE SI SERVICII</t>
+          <t>70.02.50</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Alte servicii in domeniile locuintelor, serviciilor si dezvoltarii comunale</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4359,11 +4397,11 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>9800</v>
+        <v>40237</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4374,17 +4412,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ALTE TRANSFERURI Din total capitol :</t>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>PROTECTIA MEDIULUI</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4392,11 +4425,11 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>128</v>
+        <v>9928</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4407,12 +4440,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>74.02.05</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Salubritate si gestiunea deseurilor</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>CHELTUIELI MATERIALE SI SERVICII</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4420,11 +4458,11 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G128" s="3" t="n">
-        <v>9128</v>
+        <v>9800</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4435,12 +4473,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>74.02.06</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Canalizarea si tratarea apelor reziduale</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>ALTE TRANSFERURI Din total capitol :</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4448,11 +4491,11 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>800</v>
+        <v>128</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4463,12 +4506,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ACTIUNI GENERALE ECONOMICE, COMERCIALE SI DE MUNCA</t>
+          <t>74.02.05</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Salubritate si gestiunea deseurilor</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4480,7 +4523,7 @@
         </is>
       </c>
       <c r="G130" s="3" t="n">
-        <v>1510</v>
+        <v>9128</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4491,79 +4534,83 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>74.02.06</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Canalizarea si tratarea apelor reziduale</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>80.02</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>ACTIUNI GENERALE ECONOMICE, COMERCIALE SI DE MUNCA</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>1510</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>80.02</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>ALTE TRANSFERURI</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>3</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>58.71</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="n"/>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>PROGRAME CU FINANTARE NERAMBURSABILA CHELTUIELI DE CAPITAL</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="n"/>
-      <c r="E132" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="n">
-        <v>1510</v>
-      </c>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>code 58.71 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Din total capitol :</t>
-        </is>
-      </c>
       <c r="E133" t="n">
-        <v>4</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
       <c r="G133" s="3" t="n"/>
       <c r="H133" t="inlineStr">
         <is>
@@ -4574,22 +4621,18 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>80.02.01.10</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Programe de dezvoltare regionala si sociala</t>
+          <t>58.71</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAME CU FINANTARE NERAMBURSABILA CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" s="3" t="n">
         <v>1510</v>
       </c>
@@ -4600,54 +4643,31 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="n"/>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>TRANSPORTURI</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="n"/>
-      <c r="E135" s="6" t="n">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Din total capitol</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
         <v>4</v>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="n">
-        <v>38453.5</v>
-      </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>84.02 total_2026: parent 38.453,50 != sum(children) 2.000,00 (1 children)</t>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>BUNURI SI SERVICII</t>
+          <t>80.02.01.10</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Programe de dezvoltare regionala si sociala</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4655,94 +4675,90 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G136" s="3" t="n">
+        <v>1510</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="n"/>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>TRANSPORTURI</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="n"/>
+      <c r="E137" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>38453.5</v>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>84.02 total_2026: parent 38.453,50 != sum(children) 2.000,00 (1 children)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>BUNURI SI SERVICII</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
         <v>11000</v>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>SUBVENTII</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>4</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>Ssue  r d oee aee u nr</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="n"/>
-      <c r="E138" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I138" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (46%): 'Ssue  r d oee aee u nr' vs 'Subvenţii pentru acoperirea diferenţelor'</t>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4750,9 +4766,9 @@
           <t>84.02</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Proiecte cu finantare din Fonduri exteme nerambursabile (FEN) postaderare</t>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>SUBVENTII</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -4764,7 +4780,7 @@
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>29</v>
+        <v>10000</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -4772,32 +4788,18 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
+    <row r="140" ht="30" customHeight="1">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Subvenţii pentru acoperirea diferenţelor de preţ şi tarif 40.03</t>
         </is>
       </c>
       <c r="E140" t="n">
         <v>4</v>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" s="3" t="n">
-        <v>9219</v>
+        <v>10000</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -4805,54 +4807,53 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE CAPITAL Din total capitol :</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="n"/>
-      <c r="E141" s="4" t="n">
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
         <v>4</v>
       </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="n">
-        <v>8205.5</v>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (33%): 'CHELTUIELI DE CAPITAL Din total capitol ' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="30" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>84.02.03.02</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Transport in comun</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -4860,11 +4861,11 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G142" s="3" t="n">
-        <v>19719</v>
+        <v>9219</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -4873,42 +4874,53 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>84.02.03.03</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Strazi</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>CHELTUIELI DE CAPITAL Din total capitol</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>16734.5</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="n">
+        <v>8205.5</v>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (34%): 'CHELTUIELI DE CAPITAL Din total capitol' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>84.02.50</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Alte cheltuieli in domeniul transporturilor</t>
+          <t>84.02.03.02</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>Transport in comun</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4920,42 +4932,102 @@
         </is>
       </c>
       <c r="G144" s="3" t="n">
+        <v>19719</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>84.02.03.03</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>Strazi</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>4</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>16734.5</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>84.02.50</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Alte cheltuieli în domeniul transporturilor</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>4</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>96.02</t>
         </is>
       </c>
-      <c r="B145" s="4" t="n"/>
-      <c r="C145" s="4" t="inlineStr"/>
-      <c r="D145" s="4" t="n"/>
-      <c r="E145" s="4" t="n">
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>EXCEDENT/</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G145" s="5" t="n">
+      <c r="G147" s="6" t="n">
         <v>-1202.43</v>
       </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I145" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Partea a VII-a REZERVE, EXCEDENT/DEFICIT'</t>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (37%): 'EXCEDENT/' vs 'Partea a VII-a REZERVE, EXCEDENT/DEFICIT'</t>
         </is>
       </c>
     </row>
@@ -4970,7 +5042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5059,7 +5131,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
+          <t>name mismatch vs nomenclator (31%): '_Sume aferente TVA' vs 'Finantare publica naționala'</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5156,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume aferente TVA' vs 'Finantare publica naționala'</t>
+          <t>name mismatch vs nomenclator (31%): '_Sume aferente TVA' vs 'Finantare publica naționala'</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5166,7 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -5141,25 +5213,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>unparseable cell '1.660,10 8.608,00' in column total_2026</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -5179,24 +5251,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (21%): 'COMISIOANE' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5204,24 +5276,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): 'COMISIOANE' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>61.02 total_2026: parent 11.118,00 != sum(children) 584,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5229,17 +5306,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 11.118,00 != sum(children) 584,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (16%): 'FOND HANDICAP' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5331,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (16%): 'FOND HANDICAP' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5356,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (30%): 'AJUTOARE SOCIALE - finanțarea drepturilo' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5381,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'AJUTOARE SOCIALE - finanțarea drepturilo' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5396,7 @@
           <t>V4_hierarchy</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -5344,7 +5416,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 16.992,00 != sum(children) 6.975,00 (1 children)</t>
+          <t>66.02 total_2026: parent 16.992,00 != sum(children) 10.002,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5448,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5389,12 +5461,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>code 71.85 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5476,7 @@
           <t>V4_hierarchy</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -5559,7 +5631,7 @@
           <t>V4_hierarchy</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -5664,7 +5736,7 @@
           <t>V4_hierarchy</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -5694,7 +5766,7 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -5716,12 +5788,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5729,74 +5801,79 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>code 60.61 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'CHELTUIELI DE CAPITAL' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>84.02 total_2026: parent 38.453,50 != sum(children) 2.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>58.71</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>code 58.71 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (34%): 'CHELTUIELI DE CAPITAL Din total capitol' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -5804,92 +5881,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 38.453,50 != sum(children) 2.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (46%): 'Ssue  r d oee aee u nr' vs 'Subvenţii pentru acoperirea diferenţelor'</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (33%): 'CHELTUIELI DE CAPITAL Din total capitol ' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>96.02</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Partea a VII-a REZERVE, EXCEDENT/DEFICIT'</t>
+          <t>name mismatch vs nomenclator (37%): 'EXCEDENT/' vs 'Partea a VII-a REZERVE, EXCEDENT/DEFICIT'</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5909,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Fisier</t>
         </is>
@@ -5924,17 +5921,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Metrica de calitate</t>
         </is>
@@ -5946,7 +5943,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Recall masurat</t>
         </is>
@@ -5958,7 +5955,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Documente</t>
         </is>
@@ -5968,67 +5965,67 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>% linii strict verificate</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76.7</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Celule numerice</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Celule numerice strict verificate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>% celule numerice strict verificate</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Pagini asteptate</t>
         </is>
@@ -6038,7 +6035,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Pagini selectate</t>
         </is>
@@ -6048,7 +6045,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Pagini procesate</t>
         </is>
@@ -6058,7 +6055,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>PDF complet</t>
         </is>
@@ -6070,47 +6067,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Linii fara probleme</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>% curat</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76.7</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Erori</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Avertismente</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Informatii</t>
         </is>
@@ -6120,7 +6117,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Schema publicare</t>
         </is>
@@ -6130,19 +6127,19 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>fd5cdbde2e0077d9091cceb6</t>
+          <t>83299a7720029c7de2d1c4cc</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>SHA-256 PDF sursa</t>
         </is>
@@ -6154,14 +6151,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>local, pag. 1-4, 144 linii</t>
+          <t>local, pag. 1-4, 146 linii</t>
         </is>
       </c>
     </row>
